--- a/data/trans_orig/P36B02_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B02_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>435055</t>
+          <t>432265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>455469</t>
+          <t>454994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>290403</t>
+          <t>290535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>302597</t>
+          <t>302562</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>730962</t>
+          <t>731349</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>754245</t>
+          <t>754452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>41511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26212</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>49108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>327923</t>
+          <t>328647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>348972</t>
+          <t>349619</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>336768</t>
+          <t>336216</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>355907</t>
+          <t>355539</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>673588</t>
+          <t>671288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>701224</t>
+          <t>701174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17962</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39011</t>
+          <t>38287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15958</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35097</t>
+          <t>35649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37575</t>
+          <t>37625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65211</t>
+          <t>67511</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>482621</t>
+          <t>482800</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>508439</t>
+          <t>508797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144710</t>
+          <t>144033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159020</t>
+          <t>158897</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>633330</t>
+          <t>636242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>664389</t>
+          <t>664266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33068</t>
+          <t>32710</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58886</t>
+          <t>58707</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>23749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44900</t>
+          <t>45023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75959</t>
+          <t>73047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1119007</t>
+          <t>1116172</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1157747</t>
+          <t>1156550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>658605</t>
+          <t>660591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>685244</t>
+          <t>684975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1787627</t>
+          <t>1785779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1834890</t>
+          <t>1832302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80587</t>
+          <t>81784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119327</t>
+          <t>122162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>53694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117730</t>
+          <t>120318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164993</t>
+          <t>166841</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>313227</t>
+          <t>312530</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>332656</t>
+          <t>332275</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>521415</t>
+          <t>523988</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>546042</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>843958</t>
+          <t>842524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>875498</t>
+          <t>873666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>18280</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37328</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>20440</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46204</t>
+          <t>43631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42676</t>
+          <t>44508</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74216</t>
+          <t>75650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>280285</t>
+          <t>280806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>293328</t>
+          <t>293015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1158894</t>
+          <t>1157766</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1191868</t>
+          <t>1188999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1444964</t>
+          <t>1446863</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1480069</t>
+          <t>1480311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>17395</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56892</t>
+          <t>59761</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89866</t>
+          <t>90994</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66891</t>
+          <t>66649</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101996</t>
+          <t>100097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3004678</t>
+          <t>3006056</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3065145</t>
+          <t>3065903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3156092</t>
+          <t>3155321</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3212732</t>
+          <t>3209237</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6183464</t>
+          <t>6172175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6261729</t>
+          <t>6257220</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204163</t>
+          <t>203405</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>264630</t>
+          <t>263252</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>164260</t>
+          <t>167755</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>220900</t>
+          <t>221671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>384571</t>
+          <t>389080</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>462836</t>
+          <t>474125</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>391196</t>
+          <t>391915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>414708</t>
+          <t>413915</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>287848</t>
+          <t>288565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>304362</t>
+          <t>304570</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>686361</t>
+          <t>687338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>716642</t>
+          <t>715241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46015</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25702</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34119</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64400</t>
+          <t>63423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>382817</t>
+          <t>382771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>405423</t>
+          <t>405540</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>314247</t>
+          <t>313989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>329776</t>
+          <t>329421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>705971</t>
+          <t>706598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>731723</t>
+          <t>732015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35980</t>
+          <t>36026</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50837</t>
+          <t>50210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>573467</t>
+          <t>573033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>597119</t>
+          <t>597788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>236447</t>
+          <t>235186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>251013</t>
+          <t>251138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>814400</t>
+          <t>814384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>844314</t>
+          <t>843718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>31627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55948</t>
+          <t>56382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22638</t>
+          <t>23899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44186</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74100</t>
+          <t>74116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1054020</t>
+          <t>1051206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1090797</t>
+          <t>1089461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>692425</t>
+          <t>693107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>723870</t>
+          <t>723688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1756531</t>
+          <t>1755237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1804158</t>
+          <t>1804898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68212</t>
+          <t>69548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104989</t>
+          <t>107803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40821</t>
+          <t>41003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72266</t>
+          <t>71584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119542</t>
+          <t>118802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167169</t>
+          <t>168463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>460519</t>
+          <t>460806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>484365</t>
+          <t>484465</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>701644</t>
+          <t>702190</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>728578</t>
+          <t>729287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1173168</t>
+          <t>1170712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1207708</t>
+          <t>1208053</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26231</t>
+          <t>26131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50077</t>
+          <t>49790</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31958</t>
+          <t>31249</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58892</t>
+          <t>58346</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63424</t>
+          <t>63079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>97964</t>
+          <t>100420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>250210</t>
+          <t>249728</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>261270</t>
+          <t>262114</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1030243</t>
+          <t>1028640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1061613</t>
+          <t>1060504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1284232</t>
+          <t>1283077</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1317619</t>
+          <t>1317465</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>16240</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46715</t>
+          <t>47824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78085</t>
+          <t>79688</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56678</t>
+          <t>56832</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>90065</t>
+          <t>91220</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3161204</t>
+          <t>3157370</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3221625</t>
+          <t>3220170</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3306124</t>
+          <t>3307129</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3363015</t>
+          <t>3366118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6491342</t>
+          <t>6485092</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6574638</t>
+          <t>6572478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199371</t>
+          <t>200826</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259792</t>
+          <t>263626</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>181186</t>
+          <t>178083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>238077</t>
+          <t>237072</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>390560</t>
+          <t>392720</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>473856</t>
+          <t>480106</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>387973</t>
+          <t>388009</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>409806</t>
+          <t>409037</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>315999</t>
+          <t>314955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>333790</t>
+          <t>333761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>710085</t>
+          <t>709980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>739222</t>
+          <t>739138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>18995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40059</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>32100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35865</t>
+          <t>35949</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65002</t>
+          <t>65107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>330998</t>
+          <t>332194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>354477</t>
+          <t>354759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>338525</t>
+          <t>337907</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>356485</t>
+          <t>356546</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>677969</t>
+          <t>678672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>706314</t>
+          <t>706031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43332</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31662</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66548</t>
+          <t>65845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>452860</t>
+          <t>455060</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>482569</t>
+          <t>482976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149949</t>
+          <t>149381</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161788</t>
+          <t>161245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>609813</t>
+          <t>610309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>640582</t>
+          <t>642575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39345</t>
+          <t>38938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69054</t>
+          <t>66854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>16742</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47454</t>
+          <t>45461</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78223</t>
+          <t>77727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1021689</t>
+          <t>1019986</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1061850</t>
+          <t>1063009</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>763432</t>
+          <t>763212</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>789301</t>
+          <t>789081</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1793750</t>
+          <t>1794146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1841938</t>
+          <t>1843950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86705</t>
+          <t>85546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126866</t>
+          <t>128569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>36795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62444</t>
+          <t>62664</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132493</t>
+          <t>130481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180681</t>
+          <t>180285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>558121</t>
+          <t>557503</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>584355</t>
+          <t>585605</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>678258</t>
+          <t>677729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>704149</t>
+          <t>703635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1244198</t>
+          <t>1244187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1281230</t>
+          <t>1279372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35459</t>
+          <t>34209</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61693</t>
+          <t>62311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34095</t>
+          <t>34609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59986</t>
+          <t>60515</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76828</t>
+          <t>78686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113860</t>
+          <t>113871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>259383</t>
+          <t>258279</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>275977</t>
+          <t>275265</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1000537</t>
+          <t>1000831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1032368</t>
+          <t>1031358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1266510</t>
+          <t>1266601</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1302000</t>
+          <t>1302366</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>27897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48776</t>
+          <t>49786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80607</t>
+          <t>80313</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65319</t>
+          <t>64953</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100809</t>
+          <t>100718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3065603</t>
+          <t>3066873</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3127841</t>
+          <t>3133007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3288164</t>
+          <t>3291589</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3342049</t>
+          <t>3346396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6368603</t>
+          <t>6372788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6458358</t>
+          <t>6459469</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250979</t>
+          <t>245813</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>313217</t>
+          <t>311947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>186580</t>
+          <t>182233</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>240465</t>
+          <t>237040</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>449091</t>
+          <t>447980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>538846</t>
+          <t>534661</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>444697</t>
+          <t>487366</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>429693</t>
+          <t>467622</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>460941</t>
+          <t>501732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>385811</t>
+          <t>419975</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>373359</t>
+          <t>403876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>397966</t>
+          <t>432611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>830507</t>
+          <t>907341</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>810955</t>
+          <t>886225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>850240</t>
+          <t>926673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60515</t>
+          <t>63252</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75519</t>
+          <t>82996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61656</t>
+          <t>68436</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49501</t>
+          <t>55800</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74108</t>
+          <t>84535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>122172</t>
+          <t>131688</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102439</t>
+          <t>112356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141724</t>
+          <t>152804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>403055</t>
+          <t>433230</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>389513</t>
+          <t>418827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>415959</t>
+          <t>446435</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>329414</t>
+          <t>362658</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>317356</t>
+          <t>347974</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>339664</t>
+          <t>374152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>732469</t>
+          <t>795888</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>711497</t>
+          <t>775483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>748416</t>
+          <t>813166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>49982</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62700</t>
+          <t>64385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>53166</t>
+          <t>60485</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42916</t>
+          <t>48991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65224</t>
+          <t>75169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>102324</t>
+          <t>110467</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86377</t>
+          <t>93189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123296</t>
+          <t>130872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>612704</t>
+          <t>410913</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>572657</t>
+          <t>394091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>649410</t>
+          <t>425180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>147032</t>
+          <t>164135</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140081</t>
+          <t>154787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153453</t>
+          <t>170841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>759736</t>
+          <t>575048</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>721366</t>
+          <t>558592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>802010</t>
+          <t>591694</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55560</t>
+          <t>60699</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>46432</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>77521</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26830</t>
+          <t>32710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>75439</t>
+          <t>84061</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>67415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113809</t>
+          <t>100517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>908797</t>
+          <t>986924</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>884460</t>
+          <t>959566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>928750</t>
+          <t>1008590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>903537</t>
+          <t>777689</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>876657</t>
+          <t>759637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>940378</t>
+          <t>791982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1812333</t>
+          <t>1764613</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1776819</t>
+          <t>1733769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1871410</t>
+          <t>1792225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>126022</t>
+          <t>144919</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106069</t>
+          <t>123253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150359</t>
+          <t>172277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>74557</t>
+          <t>83522</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37716</t>
+          <t>69229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101437</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>200579</t>
+          <t>228441</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141502</t>
+          <t>200829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>236093</t>
+          <t>259285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>403505</t>
+          <t>484315</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>384844</t>
+          <t>463481</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>418983</t>
+          <t>501395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>704441</t>
+          <t>751877</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>520440</t>
+          <t>735973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>772963</t>
+          <t>765273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1107946</t>
+          <t>1236192</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>928690</t>
+          <t>1212510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1177805</t>
+          <t>1258934</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71541</t>
+          <t>83649</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56063</t>
+          <t>66569</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90202</t>
+          <t>104483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>136894</t>
+          <t>78973</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68372</t>
+          <t>65577</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>320895</t>
+          <t>94877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>208435</t>
+          <t>162622</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138576</t>
+          <t>139880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387691</t>
+          <t>186304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>211386</t>
+          <t>206605</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>193309</t>
+          <t>186648</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>225615</t>
+          <t>219307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,17 +10383,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>679100</t>
+          <t>753044</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>661095</t>
+          <t>733401</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>694444</t>
+          <t>768078</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>890486</t>
+          <t>959649</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>865556</t>
+          <t>934523</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>908909</t>
+          <t>982093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>29121</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47198</t>
+          <t>50580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,17 +10496,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>82271</t>
+          <t>91237</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66927</t>
+          <t>76203</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100276</t>
+          <t>110880</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>111392</t>
+          <t>121860</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92969</t>
+          <t>99416</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136322</t>
+          <t>146986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2984143</t>
+          <t>3009352</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2930392</t>
+          <t>2963720</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3066317</t>
+          <t>3055235</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3149334</t>
+          <t>3229378</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2927031</t>
+          <t>3193757</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3229751</t>
+          <t>3261844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6133477</t>
+          <t>6238730</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5926916</t>
+          <t>6183303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6236481</t>
+          <t>6290175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>391917</t>
+          <t>433124</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>309743</t>
+          <t>387241</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>445668</t>
+          <t>478756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>428424</t>
+          <t>406015</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>348007</t>
+          <t>373549</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>650727</t>
+          <t>441636</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>820341</t>
+          <t>839139</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>717337</t>
+          <t>787694</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1026902</t>
+          <t>894566</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
